--- a/results/reliability_eval/Llama-3-8B_P1376_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1376_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5537964245662643</v>
+        <v>0.5644432301890865</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8577476611834531</v>
+        <v>0.8443105613406787</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5535252252054151</v>
+        <v>0.5644432301890865</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8575806062548614</v>
+        <v>0.8443105613406787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4438800565853802</v>
+        <v>0.4328381869818334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8034640101352841</v>
+        <v>0.7897730814001342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9939126738058066</v>
+        <v>0.9974736742692544</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9985488355044748</v>
+        <v>0.9992661809923369</v>
       </c>
       <c r="I2" t="n">
-        <v>0.837</v>
+        <v>0.819</v>
       </c>
     </row>
   </sheetData>
